--- a/sim/resources/sample/CasinoStatsSheet.xlsx
+++ b/sim/resources/sample/CasinoStatsSheet.xlsx
@@ -34,7 +34,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -81,22 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-百分比；
-在赌场进行曝光的时候，游客来访间隔的时间=游客基础来访间隔 * 曝光度来访间隔系数
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -118,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -153,25 +138,19 @@
     <t>名称</t>
   </si>
   <si>
+    <t>地区 ID</t>
+  </si>
+  <si>
     <t>等级</t>
   </si>
   <si>
     <t>基础繁荣度</t>
   </si>
   <si>
-    <t>开启曝光所需值</t>
-  </si>
-  <si>
-    <t>曝光持续基础时长（秒）</t>
-  </si>
-  <si>
     <t>游客基础来访间隔(秒)</t>
   </si>
   <si>
-    <t>曝光度来访间隔系数</t>
-  </si>
-  <si>
-    <t>升级消耗道具</t>
+    <t>升级消耗数量</t>
   </si>
   <si>
     <t>升级产出能量</t>
@@ -183,30 +162,21 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{|}</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
+    <t>RegionID</t>
+  </si>
+  <si>
     <t>level</t>
   </si>
   <si>
     <t>Prosperity</t>
   </si>
   <si>
-    <t>ExposureValue</t>
-  </si>
-  <si>
-    <t>ViewableDuration</t>
-  </si>
-  <si>
     <t>BaseVisitInterval</t>
   </si>
   <si>
-    <t>VisitIntervalCoefficient</t>
-  </si>
-  <si>
     <t>UpgradeCost</t>
   </si>
   <si>
@@ -216,19 +186,7 @@
     <t>OfflineDuration</t>
   </si>
   <si>
-    <t>赌场</t>
-  </si>
-  <si>
-    <t>1990000_10000|1970000_1000</t>
-  </si>
-  <si>
-    <t>1990000_50000|1970000_1000</t>
-  </si>
-  <si>
-    <t>1990000_100000|1970000_1000</t>
-  </si>
-  <si>
-    <t>1990000_200000|1970000_1000</t>
+    <t>拉斯维加斯</t>
   </si>
 </sst>
 </file>
@@ -885,27 +843,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1224,24 +1173,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
-    <col min="3" max="3" width="11.875" customWidth="1"/>
-    <col min="4" max="4" width="14.5" customWidth="1"/>
-    <col min="5" max="5" width="16.25" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
-    <col min="7" max="7" width="29.25" customWidth="1"/>
-    <col min="8" max="8" width="23.375" customWidth="1"/>
-    <col min="9" max="9" width="23.625" customWidth="1"/>
-    <col min="10" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="18.75" customWidth="1"/>
-    <col min="12" max="16384" width="15.625" customWidth="1"/>
+    <col min="3" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="29.25" customWidth="1"/>
+    <col min="7" max="7" width="29.75" customWidth="1"/>
+    <col min="8" max="8" width="18.5" customWidth="1"/>
+    <col min="9" max="9" width="18.75" customWidth="1"/>
+    <col min="10" max="16382" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1260,306 +1206,256 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:9">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:9">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:11">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+    <row r="4" customHeight="1" spans="1:9">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="7"/>
     </row>
-    <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="4">
+    <row r="5" customHeight="1" spans="1:9">
+      <c r="A5" s="3">
+        <f t="shared" ref="A5:A10" si="0">C5*1000+D5</f>
+        <v>1000</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3">
+        <v>60</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:9">
+      <c r="A6" s="3">
+        <f t="shared" si="0"/>
         <v>1001</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
         <v>100</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F6" s="3">
+        <v>65</v>
+      </c>
+      <c r="G6" s="3">
         <v>1000</v>
       </c>
-      <c r="F5" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="H6" s="5">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:9">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
+        <v>1002</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>100</v>
+      </c>
+      <c r="F7" s="3">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H7" s="5">
+        <v>30</v>
+      </c>
+      <c r="I7" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:9">
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
+        <v>75</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H8" s="5">
+        <v>40</v>
+      </c>
+      <c r="I8" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:9">
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
+        <v>1004</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H9" s="5">
+        <v>50</v>
+      </c>
+      <c r="I9" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:9">
+      <c r="A10" s="3">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>85</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H10" s="5">
         <v>60</v>
       </c>
-      <c r="H5" s="4">
-        <v>90</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="8">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:11">
-      <c r="A6" s="4">
-        <v>1002</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <v>100</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2000</v>
-      </c>
-      <c r="F6" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G6" s="4">
-        <v>65</v>
-      </c>
-      <c r="H6" s="4">
-        <v>80</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="8">
-        <v>20</v>
-      </c>
-      <c r="K6" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="4">
-        <v>1003</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2</v>
-      </c>
-      <c r="D7" s="4">
-        <v>100</v>
-      </c>
-      <c r="E7" s="4">
-        <v>3000</v>
-      </c>
-      <c r="F7" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G7" s="4">
-        <v>70</v>
-      </c>
-      <c r="H7" s="4">
-        <v>75</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="8">
-        <v>30</v>
-      </c>
-      <c r="K7" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="4">
-        <v>1004</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="4">
-        <v>3</v>
-      </c>
-      <c r="D8" s="4">
-        <v>100</v>
-      </c>
-      <c r="E8" s="4">
-        <v>4000</v>
-      </c>
-      <c r="F8" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G8" s="4">
-        <v>75</v>
-      </c>
-      <c r="H8" s="4">
-        <v>70</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="8">
-        <v>40</v>
-      </c>
-      <c r="K8" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="4">
-        <v>1005</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="4">
-        <v>4</v>
-      </c>
-      <c r="D9" s="4">
-        <v>100</v>
-      </c>
-      <c r="E9" s="4">
-        <v>5000</v>
-      </c>
-      <c r="F9" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G9" s="4">
-        <v>80</v>
-      </c>
-      <c r="H9" s="4">
-        <v>60</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="8">
-        <v>50</v>
-      </c>
-      <c r="K9" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="4">
-        <v>1006</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4">
-        <v>5</v>
-      </c>
-      <c r="D10" s="4">
-        <v>100</v>
-      </c>
-      <c r="E10" s="4">
-        <v>6000</v>
-      </c>
-      <c r="F10" s="4">
-        <v>3600</v>
-      </c>
-      <c r="G10" s="4">
-        <v>85</v>
-      </c>
-      <c r="H10" s="4">
-        <v>55</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="8">
-        <v>60</v>
-      </c>
-      <c r="K10" s="6">
+      <c r="I10" s="5">
         <v>120</v>
       </c>
     </row>

--- a/sim/resources/sample/CasinoStatsSheet.xlsx
+++ b/sim/resources/sample/CasinoStatsSheet.xlsx
@@ -1299,7 +1299,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="3">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="5">
